--- a/data/PM_X_username.xlsx
+++ b/data/PM_X_username.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arnav\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A7CB876-4D07-4ADE-A6FC-9F194765EB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F071447-F246-4E54-AD49-89E55FC8774A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1E6B1039-E90F-4912-B63B-8D563E7E0B13}"/>
   </bookViews>
@@ -48,73 +48,73 @@
     <t>Cathie Wood</t>
   </si>
   <si>
-    <t>@CathieDWood</t>
-  </si>
-  <si>
     <t>CEO &amp; CIO, ARK Invest</t>
   </si>
   <si>
     <t>Meb Faber</t>
   </si>
   <si>
-    <t>@MebFaber</t>
-  </si>
-  <si>
     <t>Co-founder &amp; CIO, Cambria Investment Management</t>
   </si>
   <si>
     <t>Josh Brown</t>
   </si>
   <si>
-    <t>@ReformedBroker</t>
-  </si>
-  <si>
     <t>CEO, Ritholtz Wealth Management</t>
   </si>
   <si>
     <t>Barry Ritholtz</t>
   </si>
   <si>
-    <t>@ritholtz</t>
-  </si>
-  <si>
     <t>CIO, Ritholtz Wealth Management</t>
   </si>
   <si>
     <t>Bill Ackman</t>
   </si>
   <si>
-    <t>@BillAckman</t>
-  </si>
-  <si>
     <t>CEO, Pershing Square Capital Management</t>
   </si>
   <si>
     <t>Jim Chanos</t>
   </si>
   <si>
-    <t>@WallStCynic</t>
-  </si>
-  <si>
     <t>President, Kynikos Associates</t>
   </si>
   <si>
     <t>David Einhorn</t>
   </si>
   <si>
-    <t>@davidein</t>
-  </si>
-  <si>
     <t>Founder &amp; President, Greenlight Capital</t>
   </si>
   <si>
     <t>Chamath Palihapitiya</t>
   </si>
   <si>
-    <t>@chamath</t>
-  </si>
-  <si>
     <t>Founder &amp; CEO, Social Capital</t>
+  </si>
+  <si>
+    <t>CathieDWood</t>
+  </si>
+  <si>
+    <t>MebFaber</t>
+  </si>
+  <si>
+    <t>ReformedBroker</t>
+  </si>
+  <si>
+    <t>ritholtz</t>
+  </si>
+  <si>
+    <t>davidein</t>
+  </si>
+  <si>
+    <t>chamath</t>
+  </si>
+  <si>
+    <t>BillAckman</t>
+  </si>
+  <si>
+    <t>WallStCynic</t>
   </si>
 </sst>
 </file>
@@ -499,92 +499,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="116" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
